--- a/results.xlsx
+++ b/results.xlsx
@@ -1604,6 +1604,174 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1900,7 +2068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4336,12 +4504,294 @@
           <t>Source_0, Source_1</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
         <v>13</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>51</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:16</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:36</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>13</v>
+      </c>
+      <c r="L55" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>52</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:32</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:47</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>13</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E7197, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>13</v>
+      </c>
+      <c r="L56" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>53</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:07</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:19</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="G57" t="n">
+        <v>13</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E7197, E280117000000217F51E61ED, E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>13</v>
+      </c>
+      <c r="L57" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>54</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:42</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:52</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="G58" t="n">
+        <v>13</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61DF, E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>13</v>
+      </c>
+      <c r="L58" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>55</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:22</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:36</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="G59" t="n">
+        <v>12</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E2801170000002158BB40D89, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>13</v>
+      </c>
+      <c r="L59" t="n">
+        <v>92.3</v>
+      </c>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>56</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:55</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:07</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="G60" t="n">
+        <v>12</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>13</v>
+      </c>
+      <c r="L60" t="n">
+        <v>92.3</v>
       </c>
     </row>
   </sheetData>
@@ -4356,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F534"/>
+  <dimension ref="A1:F610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20389,6 +20839,2286 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>51</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>51</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>51</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>51</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>51</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>51</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>51</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>51</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>51</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>51</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>51</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>51</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>51</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>52</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>52</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>52</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>52</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>52</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>52</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>52</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>52</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>52</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>52</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>52</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>52</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>52</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>53</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>53</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>53</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>53</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>53</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>53</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>53</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>53</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>53</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>53</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>53</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>53</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>53</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>54</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>54</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>54</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>54</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>54</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>54</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>54</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>54</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>54</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>54</v>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>54</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>54</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>54</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>55</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>55</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>55</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>55</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>55</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>55</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>55</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>55</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>55</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>55</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>55</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>55</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>56</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>56</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>56</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>56</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:17:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>56</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>56</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>56</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>56</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>56</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>56</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>56</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>20260602-161257</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>56</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:18:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1772,6 +1772,62 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2068,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4786,12 +4842,106 @@
           <t>Source_0, Source_1</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
         <v>13</v>
       </c>
       <c r="L60" t="n">
         <v>92.3</v>
+      </c>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>57</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:14</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>13</v>
+      </c>
+      <c r="L61" t="n">
+        <v>92.3</v>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>58</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:51</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:06</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G62" t="n">
+        <v>13</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61DF, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>13</v>
+      </c>
+      <c r="L62" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4806,7 +4956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F610"/>
+  <dimension ref="A1:F635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23119,6 +23269,756 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>57</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>57</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>57</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>57</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>57</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>57</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>57</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>57</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>57</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>57</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>57</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>57</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>58</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>58</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>58</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>58</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>58</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>58</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>58</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>58</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>58</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>58</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>58</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>58</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>20260602-163046</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>antennas_vertical</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>58</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-06-02 16:32:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -513,25 +513,25 @@
         <v>20260602-143428</v>
       </c>
       <c r="B4" t="str">
-        <v>antennas_opposite</v>
+        <v>antennas_vertical</v>
       </c>
       <c r="C4" t="str">
         <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-02 14:35:18</v>
+        <v>2026-06-02 14:37:11</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-02 14:35:31</v>
+        <v>2026-06-02 14:37:19</v>
       </c>
       <c r="F4" t="str">
-        <v>13.24</v>
+        <v>7.52</v>
       </c>
       <c r="G4" t="str">
         <v>9</v>
       </c>
       <c r="H4" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E60C4, E2801170000002158BB40D84, E2801170000002158BB40D89</v>
+        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719D</v>
       </c>
       <c r="I4" t="str">
         <v>Source_0, Source_1</v>
@@ -554,25 +554,25 @@
         <v>4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-02 14:37:11</v>
+        <v>2026-06-02 14:38:30</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-02 14:37:19</v>
+        <v>2026-06-02 14:39:05</v>
       </c>
       <c r="F5" t="str">
-        <v>7.52</v>
+        <v>35.27</v>
       </c>
       <c r="G5" t="str">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5" t="str">
-        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719D</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194</v>
       </c>
       <c r="I5" t="str">
         <v>Source_0, Source_1</v>
       </c>
       <c r="K5" t="str">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L5" t="str">
         <v>100</v>
@@ -589,19 +589,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-02 14:38:30</v>
+        <v>2026-06-02 14:39:42</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-02 14:39:05</v>
+        <v>2026-06-02 14:39:57</v>
       </c>
       <c r="F6" t="str">
-        <v>35.27</v>
+        <v>14.66</v>
       </c>
       <c r="G6" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719A</v>
       </c>
       <c r="I6" t="str">
         <v>Source_0, Source_1</v>
@@ -610,7 +610,7 @@
         <v>13</v>
       </c>
       <c r="L6" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="7">
@@ -624,19 +624,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-02 14:39:42</v>
+        <v>2026-06-02 14:44:22</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-02 14:39:57</v>
+        <v>2026-06-02 14:44:34</v>
       </c>
       <c r="F7" t="str">
-        <v>14.66</v>
+        <v>12.64</v>
       </c>
       <c r="G7" t="str">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H7" t="str">
-        <v>E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719A</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61E4, E280117000000217F51E7197</v>
       </c>
       <c r="I7" t="str">
         <v>Source_0, Source_1</v>
@@ -645,12 +645,12 @@
         <v>13</v>
       </c>
       <c r="L7" t="str">
-        <v>92.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>20260602-143428</v>
+        <v>20260602-145947</v>
       </c>
       <c r="B8" t="str">
         <v>antennas_vertical</v>
@@ -659,19 +659,19 @@
         <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-02 14:44:22</v>
+        <v>2026-06-02 14:59:57</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-02 14:44:34</v>
+        <v>2026-06-02 15:00:13</v>
       </c>
       <c r="F8" t="str">
-        <v>12.64</v>
+        <v>16.76</v>
       </c>
       <c r="G8" t="str">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H8" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61E4, E280117000000217F51E7197</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E7197, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A</v>
       </c>
       <c r="I8" t="str">
         <v>Source_0, Source_1</v>
@@ -680,7 +680,7 @@
         <v>13</v>
       </c>
       <c r="L8" t="str">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -694,19 +694,19 @@
         <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-02 14:59:57</v>
+        <v>2026-06-02 15:01:35</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-02 15:00:13</v>
+        <v>2026-06-02 15:01:49</v>
       </c>
       <c r="F9" t="str">
-        <v>16.76</v>
+        <v>14.11</v>
       </c>
       <c r="G9" t="str">
         <v>13</v>
       </c>
       <c r="H9" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E7197, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E60C4</v>
       </c>
       <c r="I9" t="str">
         <v>Source_0, Source_1</v>
@@ -729,19 +729,19 @@
         <v>9</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-02 15:01:35</v>
+        <v>2026-06-02 15:03:11</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-02 15:01:49</v>
+        <v>2026-06-02 15:03:26</v>
       </c>
       <c r="F10" t="str">
-        <v>14.11</v>
+        <v>14.47</v>
       </c>
       <c r="G10" t="str">
         <v>13</v>
       </c>
       <c r="H10" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E60C4</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E2801170000002158BB40D84</v>
       </c>
       <c r="I10" t="str">
         <v>Source_0, Source_1</v>
@@ -764,19 +764,19 @@
         <v>10</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-02 15:03:11</v>
+        <v>2026-06-02 15:03:52</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-02 15:03:26</v>
+        <v>2026-06-02 15:04:03</v>
       </c>
       <c r="F11" t="str">
-        <v>14.47</v>
+        <v>10.48</v>
       </c>
       <c r="G11" t="str">
         <v>13</v>
       </c>
       <c r="H11" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E2801170000002158BB40D84</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E61DF, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E2801170000002158BB40D84</v>
       </c>
       <c r="I11" t="str">
         <v>Source_0, Source_1</v>
@@ -799,19 +799,19 @@
         <v>11</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-02 15:03:52</v>
+        <v>2026-06-02 15:04:55</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-02 15:04:03</v>
+        <v>2026-06-02 15:05:09</v>
       </c>
       <c r="F12" t="str">
-        <v>10.48</v>
+        <v>14.37</v>
       </c>
       <c r="G12" t="str">
         <v>13</v>
       </c>
       <c r="H12" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E61DF, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E2801170000002158BB40D84</v>
+        <v>E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194</v>
       </c>
       <c r="I12" t="str">
         <v>Source_0, Source_1</v>
@@ -834,19 +834,19 @@
         <v>12</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-02 15:04:55</v>
+        <v>2026-06-02 15:05:39</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-02 15:05:09</v>
+        <v>2026-06-02 15:05:52</v>
       </c>
       <c r="F13" t="str">
-        <v>14.37</v>
+        <v>12.91</v>
       </c>
       <c r="G13" t="str">
         <v>13</v>
       </c>
       <c r="H13" t="str">
-        <v>E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7197, E280117000000217F51E61ED, E2801170000002158BB40D89, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E61DF</v>
       </c>
       <c r="I13" t="str">
         <v>Source_0, Source_1</v>
@@ -869,19 +869,19 @@
         <v>13</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-02 15:05:39</v>
+        <v>2026-06-02 15:06:19</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-02 15:05:52</v>
+        <v>2026-06-02 15:06:58</v>
       </c>
       <c r="F14" t="str">
-        <v>12.91</v>
+        <v>39.34</v>
       </c>
       <c r="G14" t="str">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H14" t="str">
-        <v>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7197, E280117000000217F51E61ED, E2801170000002158BB40D89, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E61DF</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E7194</v>
       </c>
       <c r="I14" t="str">
         <v>Source_0, Source_1</v>
@@ -890,7 +890,7 @@
         <v>13</v>
       </c>
       <c r="L14" t="str">
-        <v>100</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="15">
@@ -904,19 +904,19 @@
         <v>14</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-02 15:06:19</v>
+        <v>2026-06-02 15:07:36</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-02 15:06:58</v>
+        <v>2026-06-02 15:07:48</v>
       </c>
       <c r="F15" t="str">
-        <v>39.34</v>
+        <v>12.29</v>
       </c>
       <c r="G15" t="str">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H15" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E61ED, E280117000000217F51E60C4, E2801170000002158BB40D89, E2801170000002158BB40D84, E280117000000217F51E61DF, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194</v>
       </c>
       <c r="I15" t="str">
         <v>Source_0, Source_1</v>
@@ -925,7 +925,7 @@
         <v>13</v>
       </c>
       <c r="L15" t="str">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -939,19 +939,19 @@
         <v>15</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-02 15:07:36</v>
+        <v>2026-06-02 15:08:18</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-02 15:07:48</v>
+        <v>2026-06-02 15:08:34</v>
       </c>
       <c r="F16" t="str">
-        <v>12.29</v>
+        <v>15.54</v>
       </c>
       <c r="G16" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H16" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E61ED, E280117000000217F51E60C4, E2801170000002158BB40D89, E2801170000002158BB40D84, E280117000000217F51E61DF, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E61ED</v>
       </c>
       <c r="I16" t="str">
         <v>Source_0, Source_1</v>
@@ -960,7 +960,7 @@
         <v>13</v>
       </c>
       <c r="L16" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="17">
@@ -974,19 +974,19 @@
         <v>16</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-02 15:08:18</v>
+        <v>2026-06-02 15:09:01</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-02 15:08:34</v>
+        <v>2026-06-02 15:09:15</v>
       </c>
       <c r="F17" t="str">
-        <v>15.54</v>
+        <v>13.68</v>
       </c>
       <c r="G17" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" t="str">
-        <v>E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E61ED</v>
+        <v>E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F</v>
       </c>
       <c r="I17" t="str">
         <v>Source_0, Source_1</v>
@@ -995,7 +995,7 @@
         <v>13</v>
       </c>
       <c r="L17" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -1009,19 +1009,19 @@
         <v>17</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-02 15:09:01</v>
+        <v>2026-06-02 15:09:49</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-02 15:09:15</v>
+        <v>2026-06-02 15:10:02</v>
       </c>
       <c r="F18" t="str">
-        <v>13.68</v>
+        <v>12.84</v>
       </c>
       <c r="G18" t="str">
         <v>13</v>
       </c>
       <c r="H18" t="str">
-        <v>E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F</v>
       </c>
       <c r="I18" t="str">
         <v>Source_0, Source_1</v>
@@ -1044,19 +1044,19 @@
         <v>18</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-02 15:09:49</v>
+        <v>2026-06-02 15:10:27</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-02 15:10:02</v>
+        <v>2026-06-02 15:10:43</v>
       </c>
       <c r="F19" t="str">
-        <v>12.84</v>
+        <v>15.43</v>
       </c>
       <c r="G19" t="str">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H19" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F</v>
+        <v>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E7, E2801170000002158BB40D89</v>
       </c>
       <c r="I19" t="str">
         <v>Source_0, Source_1</v>
@@ -1065,12 +1065,12 @@
         <v>13</v>
       </c>
       <c r="L19" t="str">
-        <v>100</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>20260602-145947</v>
+        <v>20260602-151630</v>
       </c>
       <c r="B20" t="str">
         <v>antennas_vertical</v>
@@ -1079,19 +1079,19 @@
         <v>19</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-02 15:10:27</v>
+        <v>2026-06-02 15:17:18</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-02 15:10:43</v>
+        <v>2026-06-02 15:17:32</v>
       </c>
       <c r="F20" t="str">
-        <v>15.43</v>
+        <v>14.34</v>
       </c>
       <c r="G20" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" t="str">
-        <v>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E7, E2801170000002158BB40D89</v>
+        <v>E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7194, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E60C4, E280117000000217F51E61E4</v>
       </c>
       <c r="I20" t="str">
         <v>Source_0, Source_1</v>
@@ -1100,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="L20" t="str">
-        <v>84.6</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="21">
@@ -1114,19 +1114,19 @@
         <v>20</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-02 15:17:18</v>
+        <v>2026-06-02 15:17:59</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-02 15:17:32</v>
+        <v>2026-06-02 15:18:19</v>
       </c>
       <c r="F21" t="str">
-        <v>14.34</v>
+        <v>19.28</v>
       </c>
       <c r="G21" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" t="str">
-        <v>E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7194, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E60C4, E280117000000217F51E61E4</v>
+        <v>E280117000000217F51E61E7, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194</v>
       </c>
       <c r="I21" t="str">
         <v>Source_0, Source_1</v>
@@ -1135,7 +1135,7 @@
         <v>13</v>
       </c>
       <c r="L21" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -1149,19 +1149,19 @@
         <v>21</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-02 15:17:59</v>
+        <v>2026-06-02 15:19:11</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-02 15:18:19</v>
+        <v>2026-06-02 15:19:25</v>
       </c>
       <c r="F22" t="str">
-        <v>19.28</v>
+        <v>14.05</v>
       </c>
       <c r="G22" t="str">
         <v>13</v>
       </c>
       <c r="H22" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F</v>
       </c>
       <c r="I22" t="str">
         <v>Source_0, Source_1</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>20260602-151630</v>
+        <v>20260602-152458</v>
       </c>
       <c r="B23" t="str">
         <v>antennas_vertical</v>
@@ -1184,19 +1184,19 @@
         <v>22</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-02 15:19:11</v>
+        <v>2026-06-02 15:25:14</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-02 15:19:25</v>
+        <v>2026-06-02 15:25:32</v>
       </c>
       <c r="F23" t="str">
-        <v>14.05</v>
+        <v>17.96</v>
       </c>
       <c r="G23" t="str">
         <v>13</v>
       </c>
       <c r="H23" t="str">
-        <v>E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F</v>
+        <v>E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D</v>
       </c>
       <c r="I23" t="str">
         <v>Source_0, Source_1</v>
@@ -1219,19 +1219,19 @@
         <v>23</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-02 15:25:14</v>
+        <v>2026-06-02 15:26:20</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-06-02 15:25:32</v>
+        <v>2026-06-02 15:26:32</v>
       </c>
       <c r="F24" t="str">
-        <v>17.96</v>
+        <v>11.93</v>
       </c>
       <c r="G24" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H24" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E61DF</v>
       </c>
       <c r="I24" t="str">
         <v>Source_0, Source_1</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="L24" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="25">
@@ -1254,19 +1254,19 @@
         <v>24</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-02 15:26:20</v>
+        <v>2026-06-02 15:28:02</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-02 15:26:32</v>
+        <v>2026-06-02 15:28:17</v>
       </c>
       <c r="F25" t="str">
-        <v>11.93</v>
+        <v>15.5</v>
       </c>
       <c r="G25" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E61DF</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D</v>
       </c>
       <c r="I25" t="str">
         <v>Source_0, Source_1</v>
@@ -1275,7 +1275,7 @@
         <v>13</v>
       </c>
       <c r="L25" t="str">
-        <v>92.3</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="26">
@@ -1289,19 +1289,19 @@
         <v>25</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-02 15:28:02</v>
+        <v>2026-06-02 15:28:53</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-06-02 15:28:17</v>
+        <v>2026-06-02 15:29:07</v>
       </c>
       <c r="F26" t="str">
-        <v>15.5</v>
+        <v>13.69</v>
       </c>
       <c r="G26" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E4</v>
       </c>
       <c r="I26" t="str">
         <v>Source_0, Source_1</v>
@@ -1310,7 +1310,7 @@
         <v>13</v>
       </c>
       <c r="L26" t="str">
-        <v>84.6</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="27">
@@ -1324,19 +1324,19 @@
         <v>26</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-02 15:28:53</v>
+        <v>2026-06-02 15:30:04</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-02 15:29:07</v>
+        <v>2026-06-02 15:30:15</v>
       </c>
       <c r="F27" t="str">
-        <v>13.69</v>
+        <v>10.32</v>
       </c>
       <c r="G27" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E4</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7194, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D89</v>
       </c>
       <c r="I27" t="str">
         <v>Source_0, Source_1</v>
@@ -1345,7 +1345,7 @@
         <v>13</v>
       </c>
       <c r="L27" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1359,19 +1359,19 @@
         <v>27</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-02 15:30:04</v>
+        <v>2026-06-02 15:30:34</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-02 15:30:15</v>
+        <v>2026-06-02 15:30:48</v>
       </c>
       <c r="F28" t="str">
-        <v>10.32</v>
+        <v>13.62</v>
       </c>
       <c r="G28" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H28" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7194, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D89</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E61E4</v>
       </c>
       <c r="I28" t="str">
         <v>Source_0, Source_1</v>
@@ -1380,7 +1380,7 @@
         <v>13</v>
       </c>
       <c r="L28" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="29">
@@ -1394,19 +1394,19 @@
         <v>28</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-02 15:30:34</v>
+        <v>2026-06-02 15:32:13</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-02 15:30:48</v>
+        <v>2026-06-02 15:32:31</v>
       </c>
       <c r="F29" t="str">
-        <v>13.62</v>
+        <v>17.89</v>
       </c>
       <c r="G29" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E7197, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E61E4</v>
+        <v>E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7197, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61DF, E280117000000217F51E61E4, E2801170000002158BB40D89</v>
       </c>
       <c r="I29" t="str">
         <v>Source_0, Source_1</v>
@@ -1415,7 +1415,7 @@
         <v>13</v>
       </c>
       <c r="L29" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -1429,19 +1429,19 @@
         <v>29</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-02 15:32:13</v>
+        <v>2026-06-02 15:32:57</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-02 15:32:31</v>
+        <v>2026-06-02 15:33:09</v>
       </c>
       <c r="F30" t="str">
-        <v>17.89</v>
+        <v>12.82</v>
       </c>
       <c r="G30" t="str">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H30" t="str">
-        <v>E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7197, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61DF, E280117000000217F51E61E4, E2801170000002158BB40D89</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E2801170000002158BB40D89</v>
       </c>
       <c r="I30" t="str">
         <v>Source_0, Source_1</v>
@@ -1450,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="L30" t="str">
-        <v>100</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="31">
@@ -1464,28 +1464,28 @@
         <v>30</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-02 15:32:57</v>
+        <v>2026-06-02 15:34:08</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-02 15:33:09</v>
+        <v>2026-06-02 15:34:24</v>
       </c>
       <c r="F31" t="str">
-        <v>12.82</v>
+        <v>15.22</v>
       </c>
       <c r="G31" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H31" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E2801170000002158BB40D89</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E7082</v>
       </c>
       <c r="I31" t="str">
         <v>Source_0, Source_1</v>
       </c>
       <c r="K31" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L31" t="str">
-        <v>84.6</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="32">
@@ -1499,28 +1499,28 @@
         <v>31</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-02 15:34:08</v>
+        <v>2026-06-02 15:35:20</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-02 15:34:24</v>
+        <v>2026-06-02 15:35:32</v>
       </c>
       <c r="F32" t="str">
-        <v>15.22</v>
+        <v>11.38</v>
       </c>
       <c r="G32" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H32" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E7082</v>
+        <v>E280117000000217F51E7197, E280117000000217F51E60C4, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E7082, E280117000000217F51E61DF, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E61E7, E2801170000002158BB40D84</v>
       </c>
       <c r="I32" t="str">
         <v>Source_0, Source_1</v>
       </c>
       <c r="K32" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L32" t="str">
-        <v>108.3</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="33">
@@ -1534,19 +1534,19 @@
         <v>32</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-02 15:35:20</v>
+        <v>2026-06-02 15:36:09</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-02 15:35:32</v>
+        <v>2026-06-02 15:36:25</v>
       </c>
       <c r="F33" t="str">
-        <v>11.38</v>
+        <v>15.28</v>
       </c>
       <c r="G33" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" t="str">
-        <v>E280117000000217F51E7197, E280117000000217F51E60C4, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E7082, E280117000000217F51E61DF, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E61E7, E2801170000002158BB40D84</v>
+        <v>E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719D</v>
       </c>
       <c r="I33" t="str">
         <v>Source_0, Source_1</v>
@@ -1555,7 +1555,7 @@
         <v>13</v>
       </c>
       <c r="L33" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -1569,19 +1569,19 @@
         <v>33</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-02 15:36:09</v>
+        <v>2026-06-02 15:37:10</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-02 15:36:25</v>
+        <v>2026-06-02 15:37:28</v>
       </c>
       <c r="F34" t="str">
-        <v>15.28</v>
+        <v>17.48</v>
       </c>
       <c r="G34" t="str">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v>E2801170000002158BB40D84, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719D</v>
+        <v>E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7194</v>
       </c>
       <c r="I34" t="str">
         <v>Source_0, Source_1</v>
@@ -1590,7 +1590,7 @@
         <v>13</v>
       </c>
       <c r="L34" t="str">
-        <v>100</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="35">
@@ -1604,19 +1604,19 @@
         <v>34</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-02 15:37:10</v>
+        <v>2026-06-02 15:37:57</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-02 15:37:28</v>
+        <v>2026-06-02 15:38:12</v>
       </c>
       <c r="F35" t="str">
-        <v>17.48</v>
+        <v>14.34</v>
       </c>
       <c r="G35" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H35" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D84, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7194</v>
+        <v>E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D</v>
       </c>
       <c r="I35" t="str">
         <v>Source_0, Source_1</v>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
       <c r="L35" t="str">
-        <v>76.9</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="36">
@@ -1639,28 +1639,28 @@
         <v>35</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-02 15:37:57</v>
+        <v>2026-06-02 15:38:50</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-06-02 15:38:12</v>
+        <v>2026-06-02 15:39:05</v>
       </c>
       <c r="F36" t="str">
-        <v>14.34</v>
+        <v>14.55</v>
       </c>
       <c r="G36" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H36" t="str">
-        <v>E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D</v>
+        <v>E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F</v>
       </c>
       <c r="I36" t="str">
-        <v>Source_0, Source_1</v>
+        <v>Source_1</v>
       </c>
       <c r="K36" t="str">
         <v>13</v>
       </c>
       <c r="L36" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
@@ -1674,28 +1674,28 @@
         <v>36</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-02 15:38:50</v>
+        <v>2026-06-02 15:40:06</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-06-02 15:39:05</v>
+        <v>2026-06-02 15:40:26</v>
       </c>
       <c r="F37" t="str">
-        <v>14.55</v>
+        <v>19.93</v>
       </c>
       <c r="G37" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H37" t="str">
-        <v>E280117000000217F51E60C4, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F</v>
+        <v>E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D84</v>
       </c>
       <c r="I37" t="str">
-        <v>Source_1</v>
+        <v>Source_0, Source_1</v>
       </c>
       <c r="K37" t="str">
         <v>13</v>
       </c>
       <c r="L37" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="38">
@@ -1709,19 +1709,19 @@
         <v>37</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-02 15:40:06</v>
+        <v>2026-06-02 15:40:53</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-06-02 15:40:26</v>
+        <v>2026-06-02 15:41:07</v>
       </c>
       <c r="F38" t="str">
-        <v>19.93</v>
+        <v>13.44</v>
       </c>
       <c r="G38" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H38" t="str">
-        <v>E280117000000217F51E61E7, E280117000000217F51E7197, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D84</v>
+        <v>E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194</v>
       </c>
       <c r="I38" t="str">
         <v>Source_0, Source_1</v>
@@ -1730,7 +1730,7 @@
         <v>13</v>
       </c>
       <c r="L38" t="str">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -1744,19 +1744,19 @@
         <v>38</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-02 15:40:53</v>
+        <v>2026-06-02 15:41:25</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-06-02 15:41:07</v>
+        <v>2026-06-02 15:41:37</v>
       </c>
       <c r="F39" t="str">
-        <v>13.44</v>
+        <v>12.12</v>
       </c>
       <c r="G39" t="str">
         <v>13</v>
       </c>
       <c r="H39" t="str">
-        <v>E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E60C4, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D</v>
       </c>
       <c r="I39" t="str">
         <v>Source_0, Source_1</v>
@@ -1779,19 +1779,19 @@
         <v>39</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-02 15:41:25</v>
+        <v>2026-06-02 15:42:46</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-06-02 15:41:37</v>
+        <v>2026-06-02 15:42:59</v>
       </c>
       <c r="F40" t="str">
-        <v>12.12</v>
+        <v>13.01</v>
       </c>
       <c r="G40" t="str">
         <v>13</v>
       </c>
       <c r="H40" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D</v>
+        <v>E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E60C4</v>
       </c>
       <c r="I40" t="str">
         <v>Source_0, Source_1</v>
@@ -1814,22 +1814,22 @@
         <v>40</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-02 15:42:46</v>
+        <v>2026-06-02 15:43:44</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-06-02 15:42:59</v>
+        <v>2026-06-02 15:43:58</v>
       </c>
       <c r="F41" t="str">
-        <v>13.01</v>
+        <v>13.77</v>
       </c>
       <c r="G41" t="str">
         <v>13</v>
       </c>
       <c r="H41" t="str">
-        <v>E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E718F, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E7197, E2801170000002158BB40D84, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E60C4</v>
+        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E719D</v>
       </c>
       <c r="I41" t="str">
-        <v>Source_0, Source_1</v>
+        <v>Source_1</v>
       </c>
       <c r="K41" t="str">
         <v>13</v>
@@ -1849,22 +1849,22 @@
         <v>41</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-02 15:43:44</v>
+        <v>2026-06-02 15:44:39</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-06-02 15:43:58</v>
+        <v>2026-06-02 15:44:53</v>
       </c>
       <c r="F42" t="str">
-        <v>13.77</v>
+        <v>13.55</v>
       </c>
       <c r="G42" t="str">
         <v>13</v>
       </c>
       <c r="H42" t="str">
-        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E7197, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E7194, E280117000000217F51E719D</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61ED</v>
       </c>
       <c r="I42" t="str">
-        <v>Source_1</v>
+        <v>Source_0, Source_1</v>
       </c>
       <c r="K42" t="str">
         <v>13</v>
@@ -1884,19 +1884,19 @@
         <v>42</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-02 15:44:39</v>
+        <v>2026-06-02 15:45:43</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-06-02 15:44:53</v>
+        <v>2026-06-02 15:45:58</v>
       </c>
       <c r="F43" t="str">
-        <v>13.55</v>
+        <v>14.67</v>
       </c>
       <c r="G43" t="str">
         <v>13</v>
       </c>
       <c r="H43" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E7197, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E61ED</v>
+        <v>E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E61E4</v>
       </c>
       <c r="I43" t="str">
         <v>Source_0, Source_1</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>20260602-152458</v>
+        <v>20260602-161257</v>
       </c>
       <c r="B44" t="str">
         <v>antennas_vertical</v>
@@ -1919,22 +1919,22 @@
         <v>43</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-02 15:45:43</v>
+        <v>2026-06-02 16:13:16</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-06-02 15:45:58</v>
+        <v>2026-06-02 16:13:36</v>
       </c>
       <c r="F44" t="str">
-        <v>14.67</v>
+        <v>19.7</v>
       </c>
       <c r="G44" t="str">
         <v>13</v>
       </c>
       <c r="H44" t="str">
-        <v>E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E7197, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E61E4</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D84</v>
       </c>
       <c r="I44" t="str">
-        <v>Source_0, Source_1</v>
+        <v>Source_1</v>
       </c>
       <c r="K44" t="str">
         <v>13</v>
@@ -1954,22 +1954,22 @@
         <v>44</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-02 16:13:16</v>
+        <v>2026-06-02 16:15:32</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-06-02 16:13:36</v>
+        <v>2026-06-02 16:15:47</v>
       </c>
       <c r="F45" t="str">
-        <v>19.7</v>
+        <v>14.4</v>
       </c>
       <c r="G45" t="str">
         <v>13</v>
       </c>
       <c r="H45" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E60C4, E280117000000217F51E7197, E2801170000002158BB40D84</v>
+        <v>E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E7197, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194</v>
       </c>
       <c r="I45" t="str">
-        <v>Source_1</v>
+        <v>Source_0, Source_1</v>
       </c>
       <c r="K45" t="str">
         <v>13</v>
@@ -1989,19 +1989,19 @@
         <v>45</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-02 16:15:32</v>
+        <v>2026-06-02 16:16:07</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-06-02 16:15:47</v>
+        <v>2026-06-02 16:16:19</v>
       </c>
       <c r="F46" t="str">
-        <v>14.4</v>
+        <v>12.05</v>
       </c>
       <c r="G46" t="str">
         <v>13</v>
       </c>
       <c r="H46" t="str">
-        <v>E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E7197, E2801170000002158BB40D84, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E7197, E280117000000217F51E61ED, E280117000000217F51E61E7</v>
       </c>
       <c r="I46" t="str">
         <v>Source_0, Source_1</v>
@@ -2024,19 +2024,19 @@
         <v>46</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-02 16:16:07</v>
+        <v>2026-06-02 16:16:42</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-06-02 16:16:19</v>
+        <v>2026-06-02 16:16:52</v>
       </c>
       <c r="F47" t="str">
-        <v>12.05</v>
+        <v>10.81</v>
       </c>
       <c r="G47" t="str">
         <v>13</v>
       </c>
       <c r="H47" t="str">
-        <v>E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E2801170000002158BB40D84, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E7197, E280117000000217F51E61ED, E280117000000217F51E61E7</v>
+        <v>E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61DF, E280117000000217F51E60C4</v>
       </c>
       <c r="I47" t="str">
         <v>Source_0, Source_1</v>
@@ -2059,19 +2059,19 @@
         <v>47</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-02 16:16:42</v>
+        <v>2026-06-02 16:17:22</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-06-02 16:16:52</v>
+        <v>2026-06-02 16:17:36</v>
       </c>
       <c r="F48" t="str">
-        <v>10.81</v>
+        <v>13.92</v>
       </c>
       <c r="G48" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="str">
-        <v>E2801170000002158BB40D89, E280117000000217F51E718F, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61ED, E280117000000217F51E61E7, E2801170000002158BB40D84, E280117000000217F51E7197, E280117000000217F51E61E4, E280117000000217F51E61DF, E280117000000217F51E60C4</v>
+        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E2801170000002158BB40D89, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61E4</v>
       </c>
       <c r="I48" t="str">
         <v>Source_0, Source_1</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="L48" t="str">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="49">
@@ -2094,19 +2094,19 @@
         <v>48</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-02 16:17:22</v>
+        <v>2026-06-02 16:17:55</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-06-02 16:17:36</v>
+        <v>2026-06-02 16:18:07</v>
       </c>
       <c r="F49" t="str">
-        <v>13.92</v>
+        <v>12.62</v>
       </c>
       <c r="G49" t="str">
         <v>12</v>
       </c>
       <c r="H49" t="str">
-        <v>E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E2801170000002158BB40D89, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61E4</v>
+        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7194</v>
       </c>
       <c r="I49" t="str">
         <v>Source_0, Source_1</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>20260602-161257</v>
+        <v>20260602-163046</v>
       </c>
       <c r="B50" t="str">
         <v>antennas_vertical</v>
@@ -2129,19 +2129,19 @@
         <v>49</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-02 16:17:55</v>
+        <v>2026-06-02 16:31:00</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-06-02 16:18:07</v>
+        <v>2026-06-02 16:31:14</v>
       </c>
       <c r="F50" t="str">
-        <v>12.62</v>
+        <v>14.04</v>
       </c>
       <c r="G50" t="str">
         <v>12</v>
       </c>
       <c r="H50" t="str">
-        <v>E2801170000002158BB40D84, E280117000000217F51E61E7, E280117000000217F51E61ED, E280117000000217F51E61E4, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E60C4, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E7194</v>
+        <v>E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D84</v>
       </c>
       <c r="I50" t="str">
         <v>Source_0, Source_1</v>
@@ -2153,44 +2153,9 @@
         <v>92.3</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>20260602-163046</v>
-      </c>
-      <c r="B51" t="str">
-        <v>antennas_vertical</v>
-      </c>
-      <c r="C51" t="str">
-        <v>50</v>
-      </c>
-      <c r="D51" t="str">
-        <v>2026-06-02 16:31:00</v>
-      </c>
-      <c r="E51" t="str">
-        <v>2026-06-02 16:31:14</v>
-      </c>
-      <c r="F51" t="str">
-        <v>14.04</v>
-      </c>
-      <c r="G51" t="str">
-        <v>12</v>
-      </c>
-      <c r="H51" t="str">
-        <v>E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E7082, E280117000000217F51E718F, E280117000000217F51E7194, E2801170000002158BB40D89, E280117000000217F51E61DF, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E61E7, E280117000000217F51E60C4, E2801170000002158BB40D84</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Source_0, Source_1</v>
-      </c>
-      <c r="K51" t="str">
-        <v>13</v>
-      </c>
-      <c r="L51" t="str">
-        <v>92.3</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1543,6 +1543,202 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1019175" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1876,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7108,12 +7304,341 @@
           <t>Source_0, Source_1</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>13</v>
       </c>
       <c r="L101" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="102" ht="64" customHeight="1">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:55:54</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:53</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>59.27</v>
+      </c>
+      <c r="G102" t="n">
+        <v>6</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4, E280117000000217F51E61E4, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D84, E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>13</v>
+      </c>
+      <c r="L102" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="103" ht="64" customHeight="1">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:10</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:26</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="G103" t="n">
+        <v>13</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197, E280117000000217F51E61DF, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E61ED, E280117000000217F51E719A, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719D, E280117000000217F51E60C4, E280117000000217F51E61E7, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>13</v>
+      </c>
+      <c r="L103" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:23</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:38</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="G104" t="n">
+        <v>13</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7, E2801170000002158BB40D89, E280117000000217F51E61ED, E280117000000217F51E719D, E280117000000217F51E719A, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E7082, E280117000000217F51E61DF, E280117000000217F51E60C4, E280117000000217F51E7197, E280117000000217F51E61E4, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>13</v>
+      </c>
+      <c r="L104" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" ht="64" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:36</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:57</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="G105" t="n">
+        <v>9</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84, E280117000000217F51E7197, E280117000000217F51E60C4, E280117000000217F51E61E7, E280117000000217F51E718F, E280117000000217F51E7194, E280117000000217F51E7082, E280117000000217F51E719A, E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>13</v>
+      </c>
+      <c r="L105" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="106" ht="64" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:45</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="G106" t="n">
+        <v>13</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E61E7, E280117000000217F51E61ED, E2801170000002158BB40D89, E280117000000217F51E61E4, E280117000000217F51E7197, E280117000000217F51E61DF, E280117000000217F51E60C4, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>13</v>
+      </c>
+      <c r="L106" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" ht="64" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>6</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:25</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:37</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="G107" t="n">
+        <v>13</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF, E280117000000217F51E61ED, E280117000000217F51E60C4, E280117000000217F51E7197, E280117000000217F51E61E4, E2801170000002158BB40D89, E280117000000217F51E61E7, E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E719D, E280117000000217F51E718F, E280117000000217F51E719A, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>13</v>
+      </c>
+      <c r="L107" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" ht="64" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:53</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>7</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082, E280117000000217F51E7194, E280117000000217F51E718F, E280117000000217F51E719A, E280117000000217F51E719D, E280117000000217F51E61E4, E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Source_0, Source_1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>13</v>
+      </c>
+      <c r="L108" t="n">
+        <v>53.8</v>
       </c>
     </row>
   </sheetData>
@@ -7128,7 +7653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1265"/>
+  <dimension ref="A1:F1339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46351,6 +46876,2226 @@
         </is>
       </c>
     </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:55:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:55:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:00:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61DF</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61ED</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E60C4</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7197</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D89</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E7</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7082</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E7194</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E718F</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719A</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Source_0</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E719D</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>E280117000000217F51E61E4</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>20260603-105246</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>antennas_opposite</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>E2801170000002158BB40D84</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Source_1</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
